--- a/exports/ANANDRATHI_full_report.xlsx
+++ b/exports/ANANDRATHI_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q50"/>
+  <dimension ref="A1:U50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>8.720000000000001</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44595.55208333334</v>
+        <v>44596.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>146.8</v>
+        <v>144.5</v>
       </c>
       <c r="I2" t="n">
         <v>144.6158819667602</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.17</v>
+        <v>-4.68</v>
       </c>
       <c r="L2" t="n">
         <v>5.8</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>7.48</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44642.38541666666</v>
+        <v>44642.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>145.5</v>
+        <v>146.7</v>
       </c>
       <c r="I3" t="n">
         <v>146.5952746559818</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>46</v>
+        <v>46.16666666666666</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.52</v>
       </c>
       <c r="L3" t="n">
         <v>6.16</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>5.41</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44686.55208333334</v>
+        <v>44687.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>158</v>
+        <v>155.7</v>
       </c>
       <c r="I4" t="n">
         <v>157.6217537732483</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>44</v>
+        <v>44.83333333333334</v>
       </c>
       <c r="K4" t="n">
-        <v>7.7</v>
+        <v>6.13</v>
       </c>
       <c r="L4" t="n">
         <v>0.95</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>9.109999999999999</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44698.38541666666</v>
+        <v>44698.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>158.2</v>
+        <v>165.6</v>
       </c>
       <c r="I5" t="n">
         <v>164.1778671343957</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.61</v>
+        <v>-6.36</v>
       </c>
       <c r="L5" t="n">
-        <v>2.12</v>
+        <v>7.26</v>
       </c>
       <c r="M5" t="n">
         <v>2.1</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.67</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44726.38541666666</v>
+        <v>44726.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>159.8</v>
+        <v>157.6</v>
       </c>
       <c r="I6" t="n">
         <v>157.9823238913558</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>27.83333333333333</v>
+        <v>28</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.5</v>
+        <v>-4.83</v>
       </c>
       <c r="L6" t="n">
         <v>6.64</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>6.59</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44741.55208333334</v>
+        <v>44742.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>160.5</v>
+        <v>165</v>
       </c>
       <c r="I7" t="n">
         <v>164.607385455469</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.84</v>
+        <v>-4.7</v>
       </c>
       <c r="L7" t="n">
-        <v>4.7</v>
+        <v>4.82</v>
       </c>
       <c r="M7" t="n">
         <v>2.93</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>6.57</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44760.55208333334</v>
+        <v>44761.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>158.8</v>
+        <v>158</v>
       </c>
       <c r="I8" t="n">
         <v>158.2884403363032</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.76</v>
+        <v>-4.24</v>
       </c>
       <c r="L8" t="n">
-        <v>3.76</v>
+        <v>4.79</v>
       </c>
       <c r="M8" t="n">
         <v>0.61</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>6.02</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44771.55208333334</v>
+        <v>44774.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>160.2</v>
+        <v>165.1</v>
       </c>
       <c r="I9" t="n">
         <v>164.313576666866</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.39</v>
+        <v>-4.49</v>
       </c>
       <c r="L9" t="n">
-        <v>2.78</v>
+        <v>5.06</v>
       </c>
       <c r="M9" t="n">
         <v>1.25</v>
       </c>
       <c r="N9" t="n">
-        <v>1.08</v>
+        <v>2.31</v>
       </c>
       <c r="O9" t="n">
         <v>-0.57</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,25 +1109,25 @@
         <v>5.82</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>164.8</v>
+        <v>162.9</v>
       </c>
       <c r="I10" t="n">
         <v>163.9311646593473</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.18</v>
+        <v>-1.33</v>
       </c>
       <c r="L10" t="n">
         <v>3.15</v>
       </c>
       <c r="M10" t="n">
-        <v>0.24</v>
+        <v>0.49</v>
       </c>
       <c r="N10" t="n">
         <v>1.53</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>4.21</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44816.55208333334</v>
+        <v>44817.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>164.5</v>
+        <v>168.1</v>
       </c>
       <c r="I11" t="n">
         <v>166.5466831846258</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.98</v>
+        <v>-3.19</v>
       </c>
       <c r="L11" t="n">
-        <v>2.64</v>
+        <v>3.38</v>
       </c>
       <c r="M11" t="n">
         <v>1.05</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>5.18</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44902.55208333334</v>
+        <v>44903.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>174.8</v>
+        <v>172.6</v>
       </c>
       <c r="I12" t="n">
         <v>172.9772998612055</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>85.16666666666667</v>
+        <v>86</v>
       </c>
       <c r="K12" t="n">
-        <v>3.99</v>
+        <v>2.68</v>
       </c>
       <c r="L12" t="n">
         <v>2.74</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,25 +1316,25 @@
         <v>3.96</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44925.55208333334</v>
+        <v>44928.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>174.6</v>
+        <v>175.8</v>
       </c>
       <c r="I13" t="n">
         <v>175.0104968260317</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.16</v>
+        <v>-1.85</v>
       </c>
       <c r="L13" t="n">
         <v>2.38</v>
       </c>
       <c r="M13" t="n">
-        <v>0.88</v>
+        <v>1.2</v>
       </c>
       <c r="N13" t="n">
         <v>3.26</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>3.86</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44958.38541666666</v>
+        <v>44958.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>210.2</v>
+        <v>198.5</v>
       </c>
       <c r="I14" t="n">
         <v>200.2541594066444</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>30</v>
+        <v>30.16666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>19.57</v>
+        <v>12.91</v>
       </c>
       <c r="L14" t="n">
         <v>0.34</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>10.43</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44991.55208333334</v>
+        <v>44993.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>196.8</v>
+        <v>199.7</v>
       </c>
       <c r="I15" t="n">
         <v>198.9869652202078</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>33</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K15" t="n">
-        <v>0.86</v>
+        <v>-0.6</v>
       </c>
       <c r="L15" t="n">
         <v>5.89</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>6.92</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45061.38541666666</v>
+        <v>45061.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>216.2</v>
+        <v>210.2</v>
       </c>
       <c r="I16" t="n">
         <v>211.5986231526274</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>68</v>
+        <v>68.16666666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>8.26</v>
+        <v>5.26</v>
       </c>
       <c r="L16" t="n">
         <v>3.76</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>6.12</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45089.38541666666</v>
+        <v>45089.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>218.6</v>
+        <v>219.2</v>
       </c>
       <c r="I17" t="n">
         <v>219.1324817894262</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>27.83333333333333</v>
+        <v>28</v>
       </c>
       <c r="K17" t="n">
-        <v>-4</v>
+        <v>-4.28</v>
       </c>
       <c r="L17" t="n">
-        <v>4.38</v>
+        <v>4.42</v>
       </c>
       <c r="M17" t="n">
         <v>0.85</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>3.18</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45180.38541666666</v>
+        <v>45180.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>345.2</v>
+        <v>342.5</v>
       </c>
       <c r="I18" t="n">
         <v>343.0153799555073</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>90.83333333333333</v>
+        <v>91</v>
       </c>
       <c r="K18" t="n">
-        <v>57.48</v>
+        <v>56.25</v>
       </c>
       <c r="L18" t="n">
         <v>2.92</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>6.19</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45184.55208333334</v>
+        <v>45187.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>352.5</v>
+        <v>366.4</v>
       </c>
       <c r="I19" t="n">
         <v>363.709070566418</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>4</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.92</v>
+        <v>-6.98</v>
       </c>
       <c r="L19" t="n">
-        <v>4.29</v>
+        <v>7.88</v>
       </c>
       <c r="M19" t="n">
         <v>0.71</v>
       </c>
       <c r="N19" t="n">
-        <v>1.45</v>
+        <v>3.97</v>
       </c>
       <c r="O19" t="n">
         <v>-0.72</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>7.42</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45306.55208333334</v>
+        <v>45307.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>670.4</v>
+        <v>656.2</v>
       </c>
       <c r="I20" t="n">
         <v>665.1075422374172</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>119.1666666666667</v>
+        <v>120</v>
       </c>
       <c r="K20" t="n">
-        <v>82.97</v>
+        <v>79.09</v>
       </c>
       <c r="L20" t="n">
         <v>3.66</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>161</v>
+        <v>162</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>8.43</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45311.55208333334</v>
+        <v>45314.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>675</v>
+        <v>708.7</v>
       </c>
       <c r="I21" t="n">
         <v>705.4842665380305</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.86</v>
+        <v>-8</v>
       </c>
       <c r="L21" t="n">
-        <v>6.92</v>
+        <v>8.02</v>
       </c>
       <c r="M21" t="n">
         <v>1.45</v>
       </c>
       <c r="N21" t="n">
-        <v>4.21</v>
+        <v>4.27</v>
       </c>
       <c r="O21" t="n">
         <v>-2.83</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>10.35</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45365.55208333334</v>
+        <v>45366.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>932.2</v>
+        <v>906.8</v>
       </c>
       <c r="I22" t="n">
         <v>919.7832933391147</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>52</v>
       </c>
       <c r="K22" t="n">
-        <v>31.54</v>
+        <v>27.95</v>
       </c>
       <c r="L22" t="n">
         <v>4.66</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>11.41</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45390.55208333334</v>
+        <v>45391.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>943.8</v>
+        <v>983.5</v>
       </c>
       <c r="I23" t="n">
         <v>948.1562936796968</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.08</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>6.31</v>
+        <v>10.8</v>
       </c>
       <c r="M23" t="n">
-        <v>1.9</v>
+        <v>5.37</v>
       </c>
       <c r="N23" t="n">
-        <v>4.26</v>
+        <v>8.58</v>
       </c>
       <c r="O23" t="n">
         <v>-0.75</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>8.68</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>1023.8</v>
+        <v>968</v>
       </c>
       <c r="I24" t="n">
         <v>1000.94930164254</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>55.16666666666666</v>
+        <v>56</v>
       </c>
       <c r="K24" t="n">
-        <v>4.1</v>
+        <v>-1.58</v>
       </c>
       <c r="L24" t="n">
-        <v>2.37</v>
+        <v>9.98</v>
       </c>
       <c r="M24" t="n">
         <v>4.2</v>
       </c>
       <c r="N24" t="n">
-        <v>4.39</v>
+        <v>6.48</v>
       </c>
       <c r="O24" t="n">
         <v>8.58</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>10.11</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45478.55208333334</v>
+        <v>45481.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>1003.5</v>
+        <v>1025.3</v>
       </c>
       <c r="I25" t="n">
         <v>1005.832298843501</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.67</v>
+        <v>-5.92</v>
       </c>
       <c r="L25" t="n">
         <v>6.8</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>6.69</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45488.38541666666</v>
+        <v>45488.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>985</v>
+        <v>975.8</v>
       </c>
       <c r="I26" t="n">
         <v>984.2107897068188</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.93</v>
+        <v>-4.83</v>
       </c>
       <c r="L26" t="n">
         <v>6.1</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45525.38541666666</v>
+        <v>45525.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>934.8</v>
+        <v>940.8</v>
       </c>
       <c r="I27" t="n">
         <v>936.0158354904452</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>36.83333333333334</v>
+        <v>37</v>
       </c>
       <c r="K27" t="n">
-        <v>4.2</v>
+        <v>3.59</v>
       </c>
       <c r="L27" t="n">
         <v>3.42</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>6.52</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45594.38541666666</v>
+        <v>45594.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>983.4</v>
+        <v>979.2</v>
       </c>
       <c r="I28" t="n">
         <v>981.7603191297626</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>68.83333333333333</v>
+        <v>69</v>
       </c>
       <c r="K28" t="n">
-        <v>4.53</v>
+        <v>4.08</v>
       </c>
       <c r="L28" t="n">
         <v>7.89</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>7.46</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45618.55208333334</v>
+        <v>45621.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>993.8</v>
+        <v>1023.8</v>
       </c>
       <c r="I29" t="n">
         <v>1020.101920735239</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>24</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.49</v>
+        <v>-4.55</v>
       </c>
       <c r="L29" t="n">
         <v>6.98</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>7.8</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45645.55208333334</v>
+        <v>45646.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1036.2</v>
+        <v>1027.1</v>
       </c>
       <c r="I30" t="n">
         <v>1034.675517811263</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K30" t="n">
-        <v>1.21</v>
+        <v>0.32</v>
       </c>
       <c r="L30" t="n">
         <v>3.28</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>6.83</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45666.55208333334</v>
+        <v>45667.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>987.1</v>
+        <v>1048.8</v>
       </c>
       <c r="I31" t="n">
         <v>1010.810748883779</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K31" t="n">
-        <v>3.89</v>
+        <v>-2.11</v>
       </c>
       <c r="L31" t="n">
-        <v>1.75</v>
+        <v>2.64</v>
       </c>
       <c r="M31" t="n">
         <v>3.37</v>
       </c>
       <c r="N31" t="n">
-        <v>2.29</v>
+        <v>4.24</v>
       </c>
       <c r="O31" t="n">
         <v>-2.32</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>12.09</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45678.55208333334</v>
+        <v>45679.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>962.8</v>
+        <v>944.8</v>
       </c>
       <c r="I32" t="n">
         <v>948.0939384554893</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K32" t="n">
-        <v>-8.199999999999999</v>
+        <v>-9.92</v>
       </c>
       <c r="L32" t="n">
-        <v>9.82</v>
+        <v>10.6</v>
       </c>
       <c r="M32" t="n">
         <v>1.33</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>9.06</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45707.55208333334</v>
+        <v>45708.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>950</v>
+        <v>960.8</v>
       </c>
       <c r="I33" t="n">
         <v>953.9029335044736</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.55</v>
+        <v>-1.69</v>
       </c>
       <c r="L33" t="n">
-        <v>2.27</v>
+        <v>2.8</v>
       </c>
       <c r="M33" t="n">
         <v>1.56</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>6.85</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45720.55208333334</v>
+        <v>45721.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1005</v>
+        <v>948.9</v>
       </c>
       <c r="I34" t="n">
         <v>958.6162991545278</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K34" t="n">
-        <v>4.6</v>
+        <v>-1.24</v>
       </c>
       <c r="L34" t="n">
-        <v>1.12</v>
+        <v>2.62</v>
       </c>
       <c r="M34" t="n">
         <v>0.62</v>
       </c>
       <c r="N34" t="n">
-        <v>3.13</v>
+        <v>6.07</v>
       </c>
       <c r="O34" t="n">
         <v>2.37</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>13.35</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45741.38541666666</v>
+        <v>45741.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>888.4</v>
+        <v>925</v>
       </c>
       <c r="I35" t="n">
         <v>903.4392379584197</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K35" t="n">
-        <v>6.38</v>
+        <v>2.52</v>
       </c>
       <c r="L35" t="n">
         <v>6.67</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,25 +2903,25 @@
         <v>10.56</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>886.2</v>
+        <v>838.8</v>
       </c>
       <c r="I36" t="n">
         <v>868.8344046161002</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>10</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>-4.19</v>
+        <v>-9.32</v>
       </c>
       <c r="L36" t="n">
-        <v>4.24</v>
+        <v>13.51</v>
       </c>
       <c r="M36" t="n">
-        <v>1.43</v>
+        <v>6.34</v>
       </c>
       <c r="N36" t="n">
         <v>3.15</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>10.2</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45790.55208333334</v>
+        <v>45791.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>880.8</v>
+        <v>890.4</v>
       </c>
       <c r="I37" t="n">
         <v>886.1574242359738</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K37" t="n">
-        <v>-5.01</v>
+        <v>-6.15</v>
       </c>
       <c r="L37" t="n">
         <v>9.539999999999999</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>6.43</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45923.55208333334</v>
+        <v>45924.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1485</v>
+        <v>1455.5</v>
       </c>
       <c r="I38" t="n">
         <v>1466.053418025892</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>132.1666666666667</v>
+        <v>133</v>
       </c>
       <c r="K38" t="n">
-        <v>66.78</v>
+        <v>63.47</v>
       </c>
       <c r="L38" t="n">
         <v>1.22</v>
@@ -2607,7 +3062,7 @@
         <v>1.36</v>
       </c>
       <c r="N38" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="O38" t="n">
         <v>1.5</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>186</v>
+        <v>187</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>5</v>
+      </c>
+      <c r="U38" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>6.41</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45938.38541666666</v>
+        <v>45938.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>1487.4</v>
+        <v>1492.5</v>
       </c>
       <c r="I39" t="n">
         <v>1490.62295945735</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K39" t="n">
-        <v>-2.19</v>
+        <v>-2.54</v>
       </c>
       <c r="L39" t="n">
         <v>4.09</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7.12</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45979.38541666666</v>
+        <v>45979.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>1492</v>
+        <v>1474.4</v>
       </c>
       <c r="I40" t="n">
         <v>1475.581310380785</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>40.83333333333334</v>
+        <v>41</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.03</v>
+        <v>-1.21</v>
       </c>
       <c r="L40" t="n">
         <v>2.68</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>6.02</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46006.38541666666</v>
+        <v>46006.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>1476.3</v>
+        <v>1495</v>
       </c>
       <c r="I41" t="n">
         <v>1485.464732726591</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>26.83333333333333</v>
+        <v>27</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.13</v>
+        <v>-1.4</v>
       </c>
       <c r="L41" t="n">
         <v>1.66</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>5.66</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>46041.55208333334</v>
+        <v>46042.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1539.4</v>
+        <v>1519</v>
       </c>
       <c r="I42" t="n">
         <v>1520.011000576844</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>35</v>
+        <v>35.83333333333334</v>
       </c>
       <c r="K42" t="n">
-        <v>2.97</v>
+        <v>1.61</v>
       </c>
       <c r="L42" t="n">
         <v>1.44</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>6.69</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46076.38541666666</v>
+        <v>46076.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>1527.5</v>
+        <v>1532</v>
       </c>
       <c r="I43" t="n">
         <v>1529.259522155596</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>34</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.86</v>
       </c>
       <c r="L43" t="n">
         <v>1.8</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>3.99</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46094.38541666666</v>
+        <v>46094.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>1525</v>
+        <v>1512.5</v>
       </c>
       <c r="I44" t="n">
         <v>1521.512117486065</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>17.83333333333333</v>
+        <v>18</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.46</v>
+        <v>-1.27</v>
       </c>
       <c r="L44" t="n">
         <v>2.35</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>6.22</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46111.55208333334</v>
+        <v>46113.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1505.2</v>
+        <v>1578.8</v>
       </c>
       <c r="I45" t="n">
         <v>1555.407835539208</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>17</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K45" t="n">
-        <v>0.48</v>
+        <v>-4.38</v>
       </c>
       <c r="L45" t="n">
-        <v>2.81</v>
+        <v>4.46</v>
       </c>
       <c r="M45" t="n">
-        <v>1.13</v>
+        <v>1.48</v>
       </c>
       <c r="N45" t="n">
-        <v>2.41</v>
+        <v>3.3</v>
       </c>
       <c r="O45" t="n">
         <v>-0.98</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46178.55208333334</v>
+        <v>46181.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1755</v>
+        <v>1731.4</v>
       </c>
       <c r="I46" t="n">
         <v>1737.105188752582</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>65.16666666666667</v>
+        <v>68</v>
       </c>
       <c r="K46" t="n">
-        <v>11.16</v>
+        <v>9.67</v>
       </c>
       <c r="L46" t="n">
         <v>3.41</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>6.98</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46190.55208333334</v>
+        <v>46191.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1790.6</v>
+        <v>1836.9</v>
       </c>
       <c r="I47" t="n">
         <v>1831.721250488681</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.42</v>
+        <v>-6.09</v>
       </c>
       <c r="L47" t="n">
-        <v>3.62</v>
+        <v>7.23</v>
       </c>
       <c r="M47" t="n">
         <v>1.43</v>
       </c>
       <c r="N47" t="n">
-        <v>0.79</v>
+        <v>1.08</v>
       </c>
       <c r="O47" t="n">
         <v>-0.06</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>6.31</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46290.38541666666</v>
+        <v>46290.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>2161.3</v>
+        <v>2130</v>
       </c>
       <c r="I48" t="n">
         <v>2150.591742131137</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>99</v>
+        <v>99.16666666666667</v>
       </c>
       <c r="K48" t="n">
-        <v>17.66</v>
+        <v>15.96</v>
       </c>
       <c r="L48" t="n">
         <v>2.94</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>139</v>
+        <v>140</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>3.44</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46316.38541666666</v>
+        <v>46316.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>2180.2</v>
+        <v>2191</v>
       </c>
       <c r="I49" t="n">
         <v>2190.926083107337</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>25.83333333333333</v>
+        <v>26</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.36</v>
+        <v>-2.86</v>
       </c>
       <c r="L49" t="n">
-        <v>2.52</v>
+        <v>3.05</v>
       </c>
       <c r="M49" t="n">
         <v>0.75</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3294,6 +3893,14 @@
       <c r="Q50" t="n">
         <v>11</v>
       </c>
+      <c r="R50" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5396,7 +6003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35.4</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="6">
@@ -5406,7 +6013,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.3</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="7">
@@ -5416,7 +6023,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>132.2</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8">
@@ -5426,7 +6033,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="9">
@@ -5436,7 +6043,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41.6</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10">
@@ -5446,7 +6053,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>73.7</v>
+        <v>74.09999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -5456,7 +6063,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -5466,7 +6073,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -5476,7 +6083,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>60.4</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="14">
@@ -5486,7 +6093,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.67</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="15">
@@ -5496,7 +6103,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12.38</v>
+        <v>10.04</v>
       </c>
     </row>
     <row r="16">
@@ -5506,7 +6113,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.05</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="17">
@@ -5516,7 +6123,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>82.97</v>
+        <v>79.09</v>
       </c>
     </row>
     <row r="18">
@@ -5526,7 +6133,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>41.7</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="19">
@@ -5536,7 +6143,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.95</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="20">
@@ -5546,7 +6153,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.42</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="21">
@@ -5556,7 +6163,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9.82</v>
+        <v>13.51</v>
       </c>
     </row>
     <row r="22">
@@ -5566,7 +6173,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -5576,7 +6183,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -5586,7 +6193,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="25">
@@ -5596,7 +6203,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.45</v>
+        <v>6.34</v>
       </c>
     </row>
     <row r="26">
@@ -5606,7 +6213,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.2</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="27">
@@ -5616,7 +6223,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.88</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="28">
@@ -5626,7 +6233,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
